--- a/dcf/BIPC.xlsx
+++ b/dcf/BIPC.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>39</v>
+        <v>39.2400016784668</v>
       </c>
     </row>
     <row r="14">
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>39</v>
+        <v>39.2400016784668</v>
       </c>
     </row>
     <row r="49">
